--- a/src/evaluation/data/processed/RES_demand_based_model.xlsx
+++ b/src/evaluation/data/processed/RES_demand_based_model.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.466</v>
+        <v>17.468</v>
       </c>
       <c r="C2" t="n">
         <v>12.08</v>
@@ -481,10 +481,10 @@
         <v>28.85</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8045014394137661</v>
+        <v>0.8171244741400642</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2497625830959165</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -497,22 +497,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.064</v>
+        <v>10.864</v>
       </c>
       <c r="C3" t="n">
-        <v>11.87</v>
+        <v>12.32</v>
       </c>
       <c r="D3" t="n">
-        <v>24.652</v>
+        <v>16.586</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4901858152316144</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2298195631528964</v>
+        <v>0.3074141048824593</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7000142918393597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.514</v>
+        <v>12.408</v>
       </c>
       <c r="C4" t="n">
-        <v>9.449999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="D4" t="n">
         <v>23.792</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1565035331065164</v>
+        <v>0.1910418213313534</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6385593825925396</v>
+        <v>0.587573385518591</v>
       </c>
     </row>
     <row r="5">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.072</v>
+        <v>17.094</v>
       </c>
       <c r="C5" t="n">
         <v>15.68</v>
@@ -556,13 +556,13 @@
         <v>27.038</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7529442554305154</v>
+        <v>0.7708487998020291</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5916429249762583</v>
+        <v>0.6112115732368897</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8705159354008862</v>
+        <v>0.8522504892367908</v>
       </c>
     </row>
     <row r="6">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.96</v>
+        <v>18.946</v>
       </c>
       <c r="C6" t="n">
         <v>19.98</v>
       </c>
       <c r="D6" t="n">
-        <v>25.286</v>
+        <v>25.23</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -587,7 +587,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7453194226096901</v>
+        <v>0.7048271363339859</v>
       </c>
     </row>
     <row r="7">
@@ -597,22 +597,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.318</v>
+        <v>11.87</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>14.856</v>
+        <v>19.184</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.1244741400643405</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1471984805318139</v>
+        <v>0.08679927667269446</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.2118395303326809</v>
       </c>
     </row>
   </sheetData>
